--- a/artfynd/A 61809-2024 artfynd.xlsx
+++ b/artfynd/A 61809-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,60 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76854856</v>
+        <v>137376193</v>
       </c>
       <c r="B2" t="n">
-        <v>57141</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björkkärret, Smedjevik naturreservat, Sm</t>
+          <t>Sigtingsryd, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554557</v>
+        <v>554563</v>
       </c>
       <c r="R2" t="n">
-        <v>6303098</v>
+        <v>6303048</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-04-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-04-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,24 +765,2400 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376193</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137376061</v>
+      </c>
+      <c r="B3" t="n">
+        <v>83499</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>308</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>554636</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6302957</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376061</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137376222</v>
+      </c>
+      <c r="B4" t="n">
+        <v>83499</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>308</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>554537</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6302965</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376222</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137376249</v>
+      </c>
+      <c r="B5" t="n">
+        <v>83499</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>308</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>554605</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6303499</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376249</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137376268</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83499</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>308</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>554481</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6303331</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376268</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137376192</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97685</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>554550</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6302988</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376192</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137376191</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92560</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>554537</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6303568</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376191</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137376224</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79602</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>554574</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6302976</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376224</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>76854856</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Björkkärret, Smedjevik naturreservat, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>554557</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6303098</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-04-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-04-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Detlef Singer</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Detlef Singer</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr">
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/76854856</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137375940</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5480</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>101377</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stekelbock</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Necydalis major</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>554682</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6303035</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137375940</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137376248</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58195</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>554577</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6303586</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376248</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137375978</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5208</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>554643</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6303011</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg, Moa Berglund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137375978</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137376223</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8459</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>554567</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6302983</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376223</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137375956</v>
+      </c>
+      <c r="B15" t="n">
+        <v>61592</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106670</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svart skogssnigel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Arion ater ater</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>554554</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6303214</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137375956</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137375953</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99329</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>554577</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6303205</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137375953</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137375962</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99329</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>554470</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6303250</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137375962</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137376060</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>554674</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6303006</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg, Moa Berglund</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376060</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137375952</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106439</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>554588</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6303183</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137375952</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137376227</v>
+      </c>
+      <c r="B20" t="n">
+        <v>103995</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>554466</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6303175</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376227</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137376255</v>
+      </c>
+      <c r="B21" t="n">
+        <v>103995</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>554673</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6303314</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376255</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137376259</v>
+      </c>
+      <c r="B22" t="n">
+        <v>103995</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>554627</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6303296</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376259</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137376226</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100072</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222306</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stjärnstarr</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carex echinata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>554467</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6303176</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376226</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137376253</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100072</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222306</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stjärnstarr</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carex echinata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sigtingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>554673</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6303313</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jonatan Strandberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137376253</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61809-2024 artfynd.xlsx
+++ b/artfynd/A 61809-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376193</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137376061</v>
       </c>
       <c r="B3" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137376222</v>
       </c>
       <c r="B4" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137376249</v>
       </c>
       <c r="B5" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>137376268</v>
       </c>
       <c r="B6" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>137376192</v>
       </c>
       <c r="B7" t="n">
-        <v>97685</v>
+        <v>97691</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>137376191</v>
       </c>
       <c r="B8" t="n">
-        <v>92560</v>
+        <v>92565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>137376224</v>
       </c>
       <c r="B9" t="n">
-        <v>79602</v>
+        <v>79607</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>137376248</v>
       </c>
       <c r="B12" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>137375956</v>
       </c>
       <c r="B15" t="n">
-        <v>61592</v>
+        <v>61596</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>137375953</v>
       </c>
       <c r="B16" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>137375962</v>
       </c>
       <c r="B17" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>137376060</v>
       </c>
       <c r="B18" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137375952</v>
       </c>
       <c r="B19" t="n">
-        <v>106439</v>
+        <v>106445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137376227</v>
       </c>
       <c r="B20" t="n">
-        <v>103995</v>
+        <v>104001</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137376255</v>
       </c>
       <c r="B21" t="n">
-        <v>103995</v>
+        <v>104001</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137376259</v>
       </c>
       <c r="B22" t="n">
-        <v>103995</v>
+        <v>104001</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>137376226</v>
       </c>
       <c r="B23" t="n">
-        <v>100072</v>
+        <v>100078</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>137376253</v>
       </c>
       <c r="B24" t="n">
-        <v>100072</v>
+        <v>100078</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 61809-2024 artfynd.xlsx
+++ b/artfynd/A 61809-2024 artfynd.xlsx
@@ -2503,7 +2503,7 @@
         <v>137375952</v>
       </c>
       <c r="B19" t="n">
-        <v>106445</v>
+        <v>106446</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137376227</v>
       </c>
       <c r="B20" t="n">
-        <v>104001</v>
+        <v>104002</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137376255</v>
       </c>
       <c r="B21" t="n">
-        <v>104001</v>
+        <v>104002</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137376259</v>
       </c>
       <c r="B22" t="n">
-        <v>104001</v>
+        <v>104002</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 61809-2024 artfynd.xlsx
+++ b/artfynd/A 61809-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376193</v>
       </c>
       <c r="B2" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137376061</v>
       </c>
       <c r="B3" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137376222</v>
       </c>
       <c r="B4" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137376249</v>
       </c>
       <c r="B5" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>137376268</v>
       </c>
       <c r="B6" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>137376192</v>
       </c>
       <c r="B7" t="n">
-        <v>97691</v>
+        <v>97703</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>137376191</v>
       </c>
       <c r="B8" t="n">
-        <v>92565</v>
+        <v>92577</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>137376224</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
+        <v>79618</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>137375953</v>
       </c>
       <c r="B16" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>137375962</v>
       </c>
       <c r="B17" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>137376060</v>
       </c>
       <c r="B18" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137375952</v>
       </c>
       <c r="B19" t="n">
-        <v>106446</v>
+        <v>106458</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137376227</v>
       </c>
       <c r="B20" t="n">
-        <v>104002</v>
+        <v>104014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137376255</v>
       </c>
       <c r="B21" t="n">
-        <v>104002</v>
+        <v>104014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137376259</v>
       </c>
       <c r="B22" t="n">
-        <v>104002</v>
+        <v>104014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>137376226</v>
       </c>
       <c r="B23" t="n">
-        <v>100078</v>
+        <v>100090</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>137376253</v>
       </c>
       <c r="B24" t="n">
-        <v>100078</v>
+        <v>100090</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 61809-2024 artfynd.xlsx
+++ b/artfynd/A 61809-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376193</v>
       </c>
       <c r="B2" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137376061</v>
       </c>
       <c r="B3" t="n">
-        <v>83515</v>
+        <v>83516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137376222</v>
       </c>
       <c r="B4" t="n">
-        <v>83515</v>
+        <v>83516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137376249</v>
       </c>
       <c r="B5" t="n">
-        <v>83515</v>
+        <v>83516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>137376268</v>
       </c>
       <c r="B6" t="n">
-        <v>83515</v>
+        <v>83516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>137376192</v>
       </c>
       <c r="B7" t="n">
-        <v>97703</v>
+        <v>97704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>137376191</v>
       </c>
       <c r="B8" t="n">
-        <v>92577</v>
+        <v>92578</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>137376224</v>
       </c>
       <c r="B9" t="n">
-        <v>79618</v>
+        <v>79619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>137375953</v>
       </c>
       <c r="B16" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>137375962</v>
       </c>
       <c r="B17" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>137376060</v>
       </c>
       <c r="B18" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137375952</v>
       </c>
       <c r="B19" t="n">
-        <v>106458</v>
+        <v>106459</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137376227</v>
       </c>
       <c r="B20" t="n">
-        <v>104014</v>
+        <v>104015</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137376255</v>
       </c>
       <c r="B21" t="n">
-        <v>104014</v>
+        <v>104015</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137376259</v>
       </c>
       <c r="B22" t="n">
-        <v>104014</v>
+        <v>104015</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>137376226</v>
       </c>
       <c r="B23" t="n">
-        <v>100090</v>
+        <v>100091</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>137376253</v>
       </c>
       <c r="B24" t="n">
-        <v>100090</v>
+        <v>100091</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 61809-2024 artfynd.xlsx
+++ b/artfynd/A 61809-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376193</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137376061</v>
       </c>
       <c r="B3" t="n">
-        <v>83516</v>
+        <v>83518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137376222</v>
       </c>
       <c r="B4" t="n">
-        <v>83516</v>
+        <v>83518</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137376249</v>
       </c>
       <c r="B5" t="n">
-        <v>83516</v>
+        <v>83518</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>137376268</v>
       </c>
       <c r="B6" t="n">
-        <v>83516</v>
+        <v>83518</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>137376192</v>
       </c>
       <c r="B7" t="n">
-        <v>97704</v>
+        <v>97707</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>137376191</v>
       </c>
       <c r="B8" t="n">
-        <v>92578</v>
+        <v>92581</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>137376224</v>
       </c>
       <c r="B9" t="n">
-        <v>79619</v>
+        <v>79621</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>137375953</v>
       </c>
       <c r="B16" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>137375962</v>
       </c>
       <c r="B17" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>137376060</v>
       </c>
       <c r="B18" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137375952</v>
       </c>
       <c r="B19" t="n">
-        <v>106459</v>
+        <v>106462</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137376227</v>
       </c>
       <c r="B20" t="n">
-        <v>104015</v>
+        <v>104018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137376255</v>
       </c>
       <c r="B21" t="n">
-        <v>104015</v>
+        <v>104018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137376259</v>
       </c>
       <c r="B22" t="n">
-        <v>104015</v>
+        <v>104018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>137376226</v>
       </c>
       <c r="B23" t="n">
-        <v>100091</v>
+        <v>100094</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>137376253</v>
       </c>
       <c r="B24" t="n">
-        <v>100091</v>
+        <v>100094</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 61809-2024 artfynd.xlsx
+++ b/artfynd/A 61809-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376193</v>
       </c>
       <c r="B2" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137376061</v>
       </c>
       <c r="B3" t="n">
-        <v>83518</v>
+        <v>83522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137376222</v>
       </c>
       <c r="B4" t="n">
-        <v>83518</v>
+        <v>83522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137376249</v>
       </c>
       <c r="B5" t="n">
-        <v>83518</v>
+        <v>83522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>137376268</v>
       </c>
       <c r="B6" t="n">
-        <v>83518</v>
+        <v>83522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>137376192</v>
       </c>
       <c r="B7" t="n">
-        <v>97707</v>
+        <v>97711</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>137376191</v>
       </c>
       <c r="B8" t="n">
-        <v>92581</v>
+        <v>92585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>137376224</v>
       </c>
       <c r="B9" t="n">
-        <v>79621</v>
+        <v>79625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>137376248</v>
       </c>
       <c r="B12" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>137375956</v>
       </c>
       <c r="B15" t="n">
-        <v>61596</v>
+        <v>61600</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>137375953</v>
       </c>
       <c r="B16" t="n">
-        <v>99351</v>
+        <v>99355</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>137375962</v>
       </c>
       <c r="B17" t="n">
-        <v>99351</v>
+        <v>99355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>137376060</v>
       </c>
       <c r="B18" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>137375952</v>
       </c>
       <c r="B19" t="n">
-        <v>106462</v>
+        <v>106468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137376227</v>
       </c>
       <c r="B20" t="n">
-        <v>104018</v>
+        <v>104023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137376255</v>
       </c>
       <c r="B21" t="n">
-        <v>104018</v>
+        <v>104023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137376259</v>
       </c>
       <c r="B22" t="n">
-        <v>104018</v>
+        <v>104023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>137376226</v>
       </c>
       <c r="B23" t="n">
-        <v>100094</v>
+        <v>100098</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>137376253</v>
       </c>
       <c r="B24" t="n">
-        <v>100094</v>
+        <v>100098</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
